--- a/vlearn-app/public/quiz_excel/Day_02_AI Product Lab _ Business Framing/Day_02_Phan_01_18_Cau.xlsx
+++ b/vlearn-app/public/quiz_excel/Day_02_AI Product Lab _ Business Framing/Day_02_Phan_01_18_Cau.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,4</t>
         </is>
       </c>
       <c r="I4" s="4" t="n">
@@ -696,7 +696,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách phát biểu có số liệu hoặc nhật ký (log) khỏi phát biểu suy đoán nguyên nhân hay giải pháp.</t>
+          <t>Dữ liệu log 37/50 hồ sơ phải nhập lại địa chỉ với trung vị 4 phút trực tiếp hỗ trợ: Điểm đau nằm ở việc nhập lại địa chỉ (a), Có 37 hồ sơ bị nhập lại trong mẫu (b), và Việc nhập lại làm tăng thời gian xử lý của nhân viên (d). Ý kiến về biểu mẫu (c) là suy đoán chủ quan.</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>60</v>
@@ -955,7 +955,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Quick win phải đồng thời có tác động đáng kể và nỗ lực tương đối thấp.</t>
+          <t>Quick win được định nghĩa là cơ hội có tác động đáng kể với nỗ lực tương đối thấp. Cơ hội B có tác động 4 (cao) và nỗ lực 2 (thấp), là quick win rõ ràng hơn Cơ hội A (tác động 5 nhưng nỗ lực 5) và C (tác động chỉ 2).</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G11" s="3" t="n"/>
       <c r="H11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>60</v>
@@ -1051,7 +1051,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So cùng một chỉ số và cùng đơn vị ở từng bước.</t>
+          <t>So sánh thời gian xử lý các bước: Nhận hồ sơ: 2 phút; Kiểm tra thủ công: 17 phút; Phê duyệt: 4 phút. Bước 'Kiểm tra thủ công' chiếm 17 phút là nút thắt (bottleneck) lớn nhất.</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,3,5</t>
         </is>
       </c>
       <c r="I12" s="4" t="n">
@@ -1103,7 +1103,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách tác vụ ngôn ngữ biến thiên khỏi phép kiểm đã có luật hoàn chỉnh.</t>
+          <t>Tác vụ phù hợp để cân nhắc AI là các tác vụ ngôn ngữ tự nhiên hoặc mẫu phức tạp: Phân loại email tự do nhiều ý định (a), Gợi ý sản phẩm cá nhân hóa từ nhiều tín hiệu hành vi (c), và Tóm tắt phản hồi ngôn ngữ tự nhiên (e). Tính VAT (b) và kiểm tra định dạng 10 chữ số (d) là logic xác định cần dùng code thuần.</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I14" s="4" t="n">
@@ -1219,7 +1219,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đánh dấu riêng từng bằng chứng: đã có hay còn thiếu.</t>
+          <t>Đánh giá mức độ sẵn sàng: Quy trình và người chịu trách nhiệm đã được ghi nhận (a), nhưng Bằng chứng đánh giá còn thiếu (b), và Mức lỗi chấp nhận được còn thiếu (c). 20 mẫu là quá ít để đại diện (d) và chưa thể triển khai ngay (e).</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,4</t>
         </is>
       </c>
       <c r="I18" s="4" t="n">
@@ -1435,7 +1435,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Kiểm tra dependency và cách merge trước khi chạy song song.</t>
+          <t>Thiết kế fan-out/fan-in song song đúng: Chạy ba phân tích song song nếu cùng nhận đầu vào chuẩn hóa (a), Định nghĩa schema đầu ra chung cho bộ tổng hợp (b), và Quy định xử lý khi một nhánh hết thời gian chờ (d).</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>240000</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1485,7 +1485,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Nhân số báo cáo, số nhánh và token của mỗi nhánh.</t>
+          <t>Tổng số nhánh = 40 báo cáo × 3 nhánh/báo cáo = 120 nhánh. Với mỗi nhánh dùng 2.000 token, tổng số token là 120 × 2.000 = 240.000 token.</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4</t>
+          <t>o3 → o2 → o4 → o1</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1539,7 +1539,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Theo luồng đầu ra → tiêu chí → phản hồi → sửa lại.</t>
+          <t>Vòng lặp Evaluator–Optimizer: Bộ sinh (Generator) tạo bản nháp (o3) -&gt; Bộ đánh giá (Evaluator) chấm theo tiêu chí (o2) -&gt; Bộ đánh giá trả phản hồi cụ thể cho các tiêu chí chưa đạt (o4) -&gt; Bộ sinh sửa đầu ra theo phản hồi (o1).</t>
         </is>
       </c>
     </row>
